--- a/saucedemo/Test cases.xlsx
+++ b/saucedemo/Test cases.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MOHAMED\job\Software Testing [ QA ]\Projects\saucedemo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99FC663A-E3E7-4E2A-BA26-FE5C96BF290B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E09CDB86-30AF-4ACF-A130-0082746E005C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" activeTab="2" xr2:uid="{A007FA3B-5C3E-4B15-A9AC-45DC79D3E82D}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" activeTab="3" xr2:uid="{A007FA3B-5C3E-4B15-A9AC-45DC79D3E82D}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
     <sheet name="Product page" sheetId="2" r:id="rId2"/>
     <sheet name="Cart" sheetId="3" r:id="rId3"/>
+    <sheet name="CheckOut" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="171">
   <si>
     <t>Test Scenario</t>
   </si>
@@ -571,6 +572,66 @@
   </si>
   <si>
     <t>The Filter does not working</t>
+  </si>
+  <si>
+    <t>CheckOut</t>
+  </si>
+  <si>
+    <t>CO001</t>
+  </si>
+  <si>
+    <t>CO002</t>
+  </si>
+  <si>
+    <t>CO003</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>Verify error msg when user enters Empty data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1- Open the product page
+2- Open the  Cart page
+3- Click the Contino button </t>
+  </si>
+  <si>
+    <t>Verify that the Last Name field accepts text input</t>
+  </si>
+  <si>
+    <t>LastName field</t>
+  </si>
+  <si>
+    <t>1-Login to the application.
+2-Add a product to the cart.
+3-Proceed to Checkout.
+4-Enter a valid First Name.
+5-Click the Last Name field.
+6-Enter a valid Last Name.</t>
+  </si>
+  <si>
+    <t>The Last Name field accepts text input</t>
+  </si>
+  <si>
+    <t>The Last Name field does not accept text input</t>
+  </si>
+  <si>
+    <t>Cancel</t>
+  </si>
+  <si>
+    <t>Verify that clicking Cancel returns the user to the Cart page</t>
+  </si>
+  <si>
+    <t>1-Open the Cart page.
+2-Click Checkout.
+3-Click the Cancel button.</t>
+  </si>
+  <si>
+    <t>The user is redirected to the Cart page</t>
+  </si>
+  <si>
+    <t>The user was redirected to the Cart page successfully</t>
   </si>
 </sst>
 </file>
@@ -1468,7 +1529,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FFEAE05-2AA3-4904-928B-B110F353CA3B}">
-  <dimension ref="H9:S26"/>
+  <dimension ref="I9:S26"/>
   <sheetFormatPr defaultColWidth="65.5546875" defaultRowHeight="99.6" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="9" max="9" width="31.5546875" customWidth="1"/>
@@ -1484,7 +1545,7 @@
     <col min="19" max="19" width="33.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="8:19" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="9:19" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I9" s="8" t="s">
         <v>0</v>
       </c>
@@ -1519,7 +1580,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="8:19" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="9:19" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I10" s="19" t="s">
         <v>66</v>
       </c>
@@ -1554,7 +1615,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="8:19" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="9:19" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I11" s="20"/>
       <c r="J11" s="1" t="s">
         <v>125</v>
@@ -1587,7 +1648,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="8:19" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="9:19" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I12" s="20"/>
       <c r="J12" s="1" t="s">
         <v>126</v>
@@ -1620,7 +1681,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="8:19" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="9:19" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I13" s="20"/>
       <c r="J13" s="1" t="s">
         <v>127</v>
@@ -1653,7 +1714,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="8:19" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="9:19" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I14" s="21" t="s">
         <v>70</v>
       </c>
@@ -1686,7 +1747,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="8:19" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="9:19" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I15" s="21"/>
       <c r="J15" s="1" t="s">
         <v>129</v>
@@ -1717,11 +1778,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="8:19" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H16">
-        <f ca="1">H10:H16</f>
-        <v>0</v>
-      </c>
+    <row r="16" spans="9:19" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I16" s="21"/>
       <c r="J16" s="1" t="s">
         <v>130</v>
@@ -2225,4 +2282,160 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9643AE81-234F-4341-BDB5-25B9CA2D02D5}">
+  <dimension ref="D1:N7"/>
+  <sheetFormatPr defaultColWidth="23.44140625" defaultRowHeight="62.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="21.21875" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" customWidth="1"/>
+    <col min="6" max="6" width="18.88671875" customWidth="1"/>
+    <col min="7" max="7" width="61.21875" customWidth="1"/>
+    <col min="8" max="8" width="46" customWidth="1"/>
+    <col min="9" max="9" width="28.21875" customWidth="1"/>
+    <col min="11" max="11" width="35.33203125" customWidth="1"/>
+    <col min="12" max="12" width="46.109375" customWidth="1"/>
+    <col min="13" max="13" width="20.44140625" customWidth="1"/>
+    <col min="14" max="14" width="19.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="4:14" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="4:14" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="4:14" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="4:14" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D4" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="4:14" ht="84" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D5" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="J5" s="13"/>
+      <c r="K5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="4:14" ht="96" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D6" s="23"/>
+      <c r="E6" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="4:14" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D7" s="23"/>
+      <c r="E7" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D5:D7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/saucedemo/Test cases.xlsx
+++ b/saucedemo/Test cases.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MOHAMED\job\Software Testing [ QA ]\Projects\saucedemo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MOHAMED\job\Software Testing [ QA ]\Projects\manual\saucedemo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E09CDB86-30AF-4ACF-A130-0082746E005C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56615483-549A-41FA-8612-77AEEC6CA4C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" activeTab="3" xr2:uid="{A007FA3B-5C3E-4B15-A9AC-45DC79D3E82D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A007FA3B-5C3E-4B15-A9AC-45DC79D3E82D}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,9 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -798,7 +801,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -815,9 +818,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -843,14 +843,38 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -866,6 +890,12 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -885,9 +915,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -925,7 +955,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1031,7 +1061,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1173,7 +1203,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1184,289 +1214,294 @@
   <dimension ref="D4:Q15"/>
   <sheetFormatPr defaultColWidth="46" defaultRowHeight="67.8" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="38.5546875" customWidth="1"/>
-    <col min="6" max="6" width="37.109375" customWidth="1"/>
-    <col min="7" max="7" width="80.5546875" customWidth="1"/>
-    <col min="12" max="12" width="48.77734375" customWidth="1"/>
-    <col min="14" max="14" width="40.44140625" customWidth="1"/>
+    <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="42.21875" style="31" customWidth="1"/>
+    <col min="8" max="8" width="43.21875" style="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="26" customWidth="1"/>
+    <col min="13" max="13" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="4:17" ht="67.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L4" s="7"/>
-    </row>
-    <row r="5" spans="4:17" s="9" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D5" s="8" t="s">
+      <c r="L4" s="6"/>
+    </row>
+    <row r="5" spans="4:17" s="8" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="D5" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="J5" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="K5" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="L5" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="M5" s="8" t="s">
+      <c r="M5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="N5" s="8" t="s">
+      <c r="N5" s="16" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="4:17" ht="67.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D6" s="16" t="s">
+    <row r="6" spans="4:17" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="D6" s="23" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K6" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="L6" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="M6" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="N6" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="4:17" ht="67.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D7" s="17"/>
+      <c r="N6" s="18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="4:17" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="D7" s="24"/>
       <c r="E7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="J7" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="K7" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="L7" s="3" t="s">
+      <c r="L7" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="M7" s="4" t="s">
+      <c r="M7" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="N7" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="4:17" ht="67.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D8" s="17"/>
+      <c r="N7" s="18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="4:17" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="D8" s="24"/>
       <c r="E8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="J8" s="11" t="s">
+      <c r="J8" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="K8" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="L8" s="3" t="s">
+      <c r="L8" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="M8" s="4" t="s">
+      <c r="M8" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="N8" s="1" t="s">
+      <c r="N8" s="18" t="s">
         <v>12</v>
       </c>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
     </row>
-    <row r="9" spans="4:17" ht="67.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D9" s="17"/>
+    <row r="9" spans="4:17" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="D9" s="24"/>
       <c r="E9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="I9" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="J9" s="11" t="s">
+      <c r="J9" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="K9" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="L9" s="3" t="s">
+      <c r="L9" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="M9" s="4" t="s">
+      <c r="M9" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="N9" s="1" t="s">
+      <c r="N9" s="18" t="s">
         <v>12</v>
       </c>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
     </row>
-    <row r="10" spans="4:17" ht="67.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D10" s="17"/>
+    <row r="10" spans="4:17" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="D10" s="24"/>
       <c r="E10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="I10" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="J10" s="11" t="s">
+      <c r="J10" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="K10" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="L10" s="3" t="s">
+      <c r="L10" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="M10" s="4" t="s">
+      <c r="M10" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="N10" s="1" t="s">
+      <c r="N10" s="18" t="s">
         <v>12</v>
       </c>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
     </row>
-    <row r="11" spans="4:17" ht="67.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D11" s="17"/>
+    <row r="11" spans="4:17" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="D11" s="24"/>
       <c r="E11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="I11" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="J11" s="11" t="s">
+      <c r="J11" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="K11" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="L11" s="3" t="s">
+      <c r="L11" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="M11" s="6" t="s">
+      <c r="M11" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="N11" s="1" t="s">
+      <c r="N11" s="18" t="s">
         <v>12</v>
       </c>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
     </row>
-    <row r="12" spans="4:17" ht="67.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D12" s="18"/>
+    <row r="12" spans="4:17" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="D12" s="25"/>
       <c r="E12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="I12" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="J12" s="11" t="s">
+      <c r="J12" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="K12" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="L12" s="3" t="s">
+      <c r="L12" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="M12" s="5" t="s">
+      <c r="M12" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="N12" s="1" t="s">
+      <c r="N12" s="18" t="s">
         <v>29</v>
       </c>
       <c r="O12" s="1"/>
@@ -1475,10 +1510,10 @@
     </row>
     <row r="13" spans="4:17" ht="67.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D13" s="1"/>
-      <c r="E13" s="10"/>
+      <c r="E13" s="9"/>
       <c r="F13" s="3"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="1"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="18"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -1490,10 +1525,10 @@
     </row>
     <row r="14" spans="4:17" ht="67.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D14" s="1"/>
-      <c r="E14" s="10"/>
+      <c r="E14" s="9"/>
       <c r="F14" s="3"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="1"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="18"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -1505,10 +1540,10 @@
     </row>
     <row r="15" spans="4:17" ht="67.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D15" s="1"/>
-      <c r="E15" s="10"/>
+      <c r="E15" s="9"/>
       <c r="F15" s="3"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="1"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="18"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -1538,7 +1573,7 @@
     <col min="12" max="12" width="83.21875" customWidth="1"/>
     <col min="13" max="13" width="54.21875" customWidth="1"/>
     <col min="14" max="14" width="55" customWidth="1"/>
-    <col min="15" max="15" width="46.109375" style="12" customWidth="1"/>
+    <col min="15" max="15" width="46.109375" style="11" customWidth="1"/>
     <col min="16" max="16" width="55.77734375" customWidth="1"/>
     <col min="17" max="17" width="80.33203125" customWidth="1"/>
     <col min="18" max="18" width="35.21875" customWidth="1"/>
@@ -1546,48 +1581,48 @@
   </cols>
   <sheetData>
     <row r="9" spans="9:19" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="J9" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="K9" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="L9" s="8" t="s">
+      <c r="L9" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="M9" s="8" t="s">
+      <c r="M9" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="N9" s="8" t="s">
+      <c r="N9" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="O9" s="8" t="s">
+      <c r="O9" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="P9" s="8" t="s">
+      <c r="P9" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="Q9" s="8" t="s">
+      <c r="Q9" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="R9" s="8" t="s">
+      <c r="R9" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="S9" s="8" t="s">
+      <c r="S9" s="7" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="9:19" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I10" s="19" t="s">
+      <c r="I10" s="26" t="s">
         <v>66</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="K10" s="10" t="s">
+      <c r="K10" s="9" t="s">
         <v>50</v>
       </c>
       <c r="L10" s="2" t="s">
@@ -1602,10 +1637,10 @@
       <c r="O10" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="P10" s="11" t="s">
+      <c r="P10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="Q10" s="11" t="s">
+      <c r="Q10" s="10" t="s">
         <v>47</v>
       </c>
       <c r="R10" s="4" t="s">
@@ -1616,11 +1651,11 @@
       </c>
     </row>
     <row r="11" spans="9:19" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I11" s="20"/>
+      <c r="I11" s="27"/>
       <c r="J11" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="K11" s="10" t="s">
+      <c r="K11" s="9" t="s">
         <v>50</v>
       </c>
       <c r="L11" s="2" t="s">
@@ -1635,10 +1670,10 @@
       <c r="O11" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="P11" s="11" t="s">
+      <c r="P11" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="Q11" s="11" t="s">
+      <c r="Q11" s="10" t="s">
         <v>49</v>
       </c>
       <c r="R11" s="4" t="s">
@@ -1649,11 +1684,11 @@
       </c>
     </row>
     <row r="12" spans="9:19" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I12" s="20"/>
+      <c r="I12" s="27"/>
       <c r="J12" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="K12" s="10" t="s">
+      <c r="K12" s="9" t="s">
         <v>50</v>
       </c>
       <c r="L12" s="2" t="s">
@@ -1668,10 +1703,10 @@
       <c r="O12" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="P12" s="11" t="s">
+      <c r="P12" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="Q12" s="11" t="s">
+      <c r="Q12" s="10" t="s">
         <v>77</v>
       </c>
       <c r="R12" s="5" t="s">
@@ -1682,11 +1717,11 @@
       </c>
     </row>
     <row r="13" spans="9:19" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I13" s="20"/>
+      <c r="I13" s="27"/>
       <c r="J13" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="K13" s="10" t="s">
+      <c r="K13" s="9" t="s">
         <v>83</v>
       </c>
       <c r="L13" s="3" t="s">
@@ -1701,10 +1736,10 @@
       <c r="O13" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="P13" s="11" t="s">
+      <c r="P13" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="Q13" s="11" t="s">
+      <c r="Q13" s="10" t="s">
         <v>86</v>
       </c>
       <c r="R13" s="5" t="s">
@@ -1715,13 +1750,13 @@
       </c>
     </row>
     <row r="14" spans="9:19" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I14" s="21" t="s">
+      <c r="I14" s="28" t="s">
         <v>70</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="K14" s="10" t="s">
+      <c r="K14" s="9" t="s">
         <v>73</v>
       </c>
       <c r="L14" s="3" t="s">
@@ -1748,11 +1783,11 @@
       </c>
     </row>
     <row r="15" spans="9:19" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I15" s="21"/>
+      <c r="I15" s="28"/>
       <c r="J15" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="K15" s="10" t="s">
+      <c r="K15" s="9" t="s">
         <v>61</v>
       </c>
       <c r="L15" s="3" t="s">
@@ -1779,11 +1814,11 @@
       </c>
     </row>
     <row r="16" spans="9:19" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I16" s="21"/>
+      <c r="I16" s="28"/>
       <c r="J16" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="K16" s="10" t="s">
+      <c r="K16" s="9" t="s">
         <v>61</v>
       </c>
       <c r="L16" s="3" t="s">
@@ -1810,11 +1845,11 @@
       </c>
     </row>
     <row r="17" spans="9:19" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I17" s="21"/>
+      <c r="I17" s="28"/>
       <c r="J17" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="K17" s="10" t="s">
+      <c r="K17" s="9" t="s">
         <v>51</v>
       </c>
       <c r="L17" s="3" t="s">
@@ -1829,7 +1864,7 @@
       <c r="O17" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="P17" s="11" t="s">
+      <c r="P17" s="10" t="s">
         <v>54</v>
       </c>
       <c r="Q17" s="3" t="s">
@@ -1843,11 +1878,11 @@
       </c>
     </row>
     <row r="18" spans="9:19" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I18" s="21"/>
+      <c r="I18" s="28"/>
       <c r="J18" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="K18" s="10" t="s">
+      <c r="K18" s="9" t="s">
         <v>51</v>
       </c>
       <c r="L18" s="3" t="s">
@@ -1876,11 +1911,11 @@
       </c>
     </row>
     <row r="19" spans="9:19" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I19" s="21"/>
+      <c r="I19" s="28"/>
       <c r="J19" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="K19" s="10" t="s">
+      <c r="K19" s="9" t="s">
         <v>67</v>
       </c>
       <c r="L19" s="3" t="s">
@@ -1906,11 +1941,11 @@
       </c>
     </row>
     <row r="20" spans="9:19" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I20" s="21"/>
+      <c r="I20" s="28"/>
       <c r="J20" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="K20" s="10" t="s">
+      <c r="K20" s="9" t="s">
         <v>81</v>
       </c>
       <c r="L20" s="3" t="s">
@@ -1936,11 +1971,11 @@
       </c>
     </row>
     <row r="21" spans="9:19" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I21" s="21"/>
+      <c r="I21" s="28"/>
       <c r="J21" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="K21" s="10" t="s">
+      <c r="K21" s="9" t="s">
         <v>87</v>
       </c>
       <c r="L21" s="3" t="s">
@@ -1969,13 +2004,13 @@
       </c>
     </row>
     <row r="22" spans="9:19" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I22" s="22" t="s">
+      <c r="I22" s="29" t="s">
         <v>71</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="K22" s="10" t="s">
+      <c r="K22" s="9" t="s">
         <v>74</v>
       </c>
       <c r="L22" s="3" t="s">
@@ -2001,11 +2036,11 @@
       </c>
     </row>
     <row r="23" spans="9:19" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I23" s="22"/>
+      <c r="I23" s="29"/>
       <c r="J23" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K23" s="10" t="s">
+      <c r="K23" s="9" t="s">
         <v>91</v>
       </c>
       <c r="L23" s="3" t="s">
@@ -2031,11 +2066,11 @@
       </c>
     </row>
     <row r="24" spans="9:19" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I24" s="22"/>
+      <c r="I24" s="29"/>
       <c r="J24" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="K24" s="10" t="s">
+      <c r="K24" s="9" t="s">
         <v>96</v>
       </c>
       <c r="L24" s="3" t="s">
@@ -2061,11 +2096,11 @@
       </c>
     </row>
     <row r="25" spans="9:19" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I25" s="22"/>
+      <c r="I25" s="29"/>
       <c r="J25" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="K25" s="10" t="s">
+      <c r="K25" s="9" t="s">
         <v>97</v>
       </c>
       <c r="L25" s="3" t="s">
@@ -2091,11 +2126,11 @@
       </c>
     </row>
     <row r="26" spans="9:19" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I26" s="22"/>
+      <c r="I26" s="29"/>
       <c r="J26" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="K26" s="10" t="s">
+      <c r="K26" s="9" t="s">
         <v>99</v>
       </c>
       <c r="L26" s="3" t="s">
@@ -2145,48 +2180,48 @@
   <sheetData>
     <row r="1" spans="3:13" ht="113.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="3:13" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="M2" s="7" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="3:13" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="30" t="s">
         <v>141</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="13" t="s">
         <v>117</v>
       </c>
       <c r="F3" s="3" t="s">
@@ -2198,7 +2233,7 @@
       <c r="H3" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="I3" s="13"/>
+      <c r="I3" s="12"/>
       <c r="J3" s="2" t="s">
         <v>120</v>
       </c>
@@ -2213,11 +2248,11 @@
       </c>
     </row>
     <row r="4" spans="3:13" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="23"/>
-      <c r="D4" s="14" t="s">
+      <c r="C4" s="30"/>
+      <c r="D4" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="13" t="s">
         <v>121</v>
       </c>
       <c r="F4" s="3" t="s">
@@ -2243,11 +2278,11 @@
       </c>
     </row>
     <row r="5" spans="3:13" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="23"/>
-      <c r="D5" s="14" t="s">
+      <c r="C5" s="30"/>
+      <c r="D5" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="13" t="s">
         <v>145</v>
       </c>
       <c r="F5" s="3" t="s">
@@ -2259,10 +2294,10 @@
       <c r="H5" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="J5" s="11" t="s">
+      <c r="J5" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="K5" s="10" t="s">
         <v>147</v>
       </c>
       <c r="L5" s="4" t="s">
@@ -2273,7 +2308,7 @@
       </c>
     </row>
     <row r="6" spans="3:13" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="15"/>
+      <c r="C6" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2305,48 +2340,48 @@
     <row r="2" spans="4:14" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="4:14" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="4:14" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="L4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="M4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="N4" s="7" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="4:14" ht="84" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="30" t="s">
         <v>154</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="13" t="s">
         <v>158</v>
       </c>
       <c r="G5" s="3" t="s">
@@ -2355,10 +2390,10 @@
       <c r="H5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="J5" s="13"/>
+      <c r="J5" s="12"/>
       <c r="K5" s="3" t="s">
         <v>13</v>
       </c>
@@ -2373,11 +2408,11 @@
       </c>
     </row>
     <row r="6" spans="4:14" ht="96" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D6" s="23"/>
-      <c r="E6" s="14" t="s">
+      <c r="D6" s="30"/>
+      <c r="E6" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="13" t="s">
         <v>162</v>
       </c>
       <c r="G6" s="3" t="s">
@@ -2386,7 +2421,7 @@
       <c r="H6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="10" t="s">
         <v>163</v>
       </c>
       <c r="K6" s="2" t="s">
@@ -2403,11 +2438,11 @@
       </c>
     </row>
     <row r="7" spans="4:14" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D7" s="23"/>
-      <c r="E7" s="14" t="s">
+      <c r="D7" s="30"/>
+      <c r="E7" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="13" t="s">
         <v>166</v>
       </c>
       <c r="G7" s="3" t="s">
@@ -2416,13 +2451,13 @@
       <c r="H7" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="K7" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="L7" s="11" t="s">
+      <c r="L7" s="10" t="s">
         <v>170</v>
       </c>
       <c r="M7" s="4" t="s">
